--- a/grupos/6BEM - Estadisticos 20232.xlsx
+++ b/grupos/6BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -203,46 +203,55 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ROBLES</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RICO</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
   </si>
   <si>
     <t>CUICAHUA</t>
   </si>
   <si>
-    <t>SINAI ANTONIO</t>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
   <si>
     <t>JORGE MARIO</t>
   </si>
   <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
   </si>
   <si>
     <t>DARINKA</t>
@@ -753,22 +762,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -801,7 +810,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -830,22 +839,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -869,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -878,10 +887,10 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -907,22 +916,22 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -943,10 +952,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -955,7 +964,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -984,22 +993,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1023,19 +1032,19 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1061,22 +1070,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1112,7 +1121,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1138,22 +1147,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1174,7 +1183,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1186,10 +1195,10 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1215,22 +1224,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1251,7 +1260,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1263,7 +1272,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1292,22 +1301,22 @@
         <v>4</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1369,22 +1378,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1405,10 +1414,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1446,22 +1455,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1482,22 +1491,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1523,22 +1532,22 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1571,10 +1580,10 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1600,22 +1609,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1639,16 +1648,16 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1677,22 +1686,22 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1754,22 +1763,22 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1805,7 +1814,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1831,22 +1840,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1908,22 +1917,22 @@
         <v>4</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1985,22 +1994,22 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2024,7 +2033,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2033,10 +2042,10 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2062,22 +2071,22 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2098,10 +2107,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2110,10 +2119,10 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,22 +2148,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2178,19 +2187,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2216,22 +2225,22 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2264,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2293,22 +2302,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2329,19 +2338,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>8</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2370,22 +2379,22 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2421,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2447,22 +2456,22 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2483,10 +2492,10 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2495,10 +2504,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2524,22 +2533,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2560,7 +2569,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2572,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2601,22 +2610,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2640,13 +2649,13 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2678,22 +2687,22 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2755,22 +2764,22 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2791,10 +2800,10 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2803,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -2832,22 +2841,22 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2868,10 +2877,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -2880,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3019,7 +3028,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3037,7 +3046,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3078,10 +3087,10 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3090,16 +3099,16 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3108,7 +3117,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3199,7 +3208,7 @@
         <v>80</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3217,7 +3226,7 @@
         <v>80</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3255,40 +3264,40 @@
         <v>64</v>
       </c>
       <c r="H8">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="I8">
+        <v>85</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>97.5</v>
+      </c>
+      <c r="L8">
+        <v>78.2</v>
+      </c>
+      <c r="M8">
+        <v>82</v>
+      </c>
+      <c r="N8">
         <v>95</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
-        <v>83.3</v>
-      </c>
-      <c r="M8">
-        <v>64</v>
-      </c>
-      <c r="N8">
-        <v>96.7</v>
-      </c>
       <c r="O8">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R8">
-        <v>83.3</v>
+        <v>78.2</v>
       </c>
       <c r="S8">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3314,7 +3323,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3332,7 +3341,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3432,10 +3441,10 @@
         <v>60</v>
       </c>
       <c r="H11">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="I11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3444,16 +3453,16 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>87.3</v>
       </c>
       <c r="M11">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N11">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3462,10 +3471,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>87.3</v>
       </c>
       <c r="S11">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3503,10 +3512,10 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -3521,10 +3530,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3550,10 +3559,10 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3565,13 +3574,13 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N13">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3583,7 +3592,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3609,10 +3618,10 @@
         <v>60</v>
       </c>
       <c r="H14">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="I14">
-        <v>85</v>
+        <v>77.5</v>
       </c>
       <c r="J14">
         <v>90</v>
@@ -3624,13 +3633,13 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N14">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>77.5</v>
       </c>
       <c r="P14">
         <v>90</v>
@@ -3642,7 +3651,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3671,37 +3680,37 @@
         <v>86.7</v>
       </c>
       <c r="I15">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="M15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N15">
         <v>86.7</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="S15">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3727,40 +3736,40 @@
         <v>56</v>
       </c>
       <c r="H16">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I16">
+        <v>12.5</v>
+      </c>
+      <c r="J16">
+        <v>7.5</v>
+      </c>
+      <c r="K16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L16">
+        <v>34.5</v>
+      </c>
+      <c r="M16">
+        <v>34</v>
+      </c>
+      <c r="N16">
         <v>25</v>
       </c>
-      <c r="J16">
-        <v>15</v>
-      </c>
-      <c r="K16">
-        <v>17.5</v>
-      </c>
-      <c r="L16">
-        <v>63.3</v>
-      </c>
-      <c r="M16">
-        <v>56</v>
-      </c>
-      <c r="N16">
-        <v>50</v>
-      </c>
       <c r="O16">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="P16">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q16">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R16">
-        <v>63.3</v>
+        <v>34.5</v>
       </c>
       <c r="S16">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3786,11 +3795,11 @@
         <v>100</v>
       </c>
       <c r="H17">
+        <v>83.3</v>
+      </c>
+      <c r="I17">
         <v>80</v>
       </c>
-      <c r="I17">
-        <v>85</v>
-      </c>
       <c r="J17">
         <v>100</v>
       </c>
@@ -3798,17 +3807,17 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N17">
+        <v>83.3</v>
+      </c>
+      <c r="O17">
         <v>80</v>
       </c>
-      <c r="O17">
-        <v>85</v>
-      </c>
       <c r="P17">
         <v>100</v>
       </c>
@@ -3816,10 +3825,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3845,40 +3854,40 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="I18">
-        <v>85</v>
+        <v>67.5</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L18">
-        <v>76.7</v>
+        <v>78.2</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N18">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="O18">
-        <v>85</v>
+        <v>67.5</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R18">
-        <v>76.7</v>
+        <v>78.2</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3904,40 +3913,40 @@
         <v>64</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M19">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O19">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S19">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4022,10 +4031,10 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4034,16 +4043,16 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4052,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4081,13 +4090,13 @@
         <v>72</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4096,16 +4105,16 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4114,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4152,7 +4161,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4170,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4208,10 +4217,10 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4226,10 +4235,10 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4261,7 +4270,7 @@
         <v>86.7</v>
       </c>
       <c r="I25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J25">
         <v>90</v>
@@ -4270,7 +4279,7 @@
         <v>95</v>
       </c>
       <c r="L25">
-        <v>73.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4279,7 +4288,7 @@
         <v>86.7</v>
       </c>
       <c r="O25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P25">
         <v>90</v>
@@ -4288,7 +4297,7 @@
         <v>95</v>
       </c>
       <c r="R25">
-        <v>73.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4320,34 +4329,34 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
+        <v>97.5</v>
+      </c>
+      <c r="L26">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>95</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>90</v>
-      </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4435,16 +4444,16 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4453,16 +4462,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4494,40 +4503,40 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I29">
+        <v>85</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>97.5</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
         <v>90</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
       <c r="N29">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O29">
+        <v>85</v>
+      </c>
+      <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>97.5</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
         <v>90</v>
-      </c>
-      <c r="P29">
-        <v>100</v>
-      </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>100</v>
-      </c>
-      <c r="S29">
-        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4553,40 +4562,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="I30">
+        <v>85</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>92.5</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30">
         <v>90</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
-      <c r="K30">
+      <c r="N30">
+        <v>83.3</v>
+      </c>
+      <c r="O30">
+        <v>85</v>
+      </c>
+      <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>92.5</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
         <v>90</v>
-      </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
-      <c r="M30">
-        <v>100</v>
-      </c>
-      <c r="N30">
-        <v>86.7</v>
-      </c>
-      <c r="O30">
-        <v>90</v>
-      </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
-      <c r="Q30">
-        <v>90</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
-      <c r="S30">
-        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4627,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -4645,7 +4654,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4711,19 +4720,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="G2" s="2">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4743,19 +4752,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>67.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4775,19 +4784,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>67.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4807,19 +4816,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4851,7 +4860,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4883,7 +4892,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4933,7 +4942,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4965,16 +4974,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920207</v>
+        <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4988,22 +4997,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920207</v>
+        <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5011,22 +5020,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920209</v>
+        <v>21330051920386</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5034,22 +5043,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920209</v>
+        <v>21330051920386</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5057,16 +5066,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920190</v>
+        <v>21330051920209</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5080,22 +5089,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920192</v>
+        <v>21330051920209</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5103,24 +5112,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920214</v>
+        <v>21330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920212</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20232.xlsx
+++ b/grupos/6BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>León González Ruth</t>
   </si>
   <si>
@@ -203,58 +203,49 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
 </sst>
 </file>
@@ -780,28 +771,28 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -857,25 +848,25 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -887,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -934,28 +925,28 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -967,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1011,40 +1002,40 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>10</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1088,28 +1079,28 @@
         <v>4</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1118,10 +1109,10 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1165,25 +1156,25 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1242,22 +1233,22 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1319,25 +1310,25 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1352,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1396,22 +1387,22 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1426,7 +1417,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1473,22 +1464,22 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1497,13 +1488,13 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1550,40 +1541,40 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1627,28 +1618,28 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1660,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1704,22 +1695,22 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1781,25 +1772,25 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1811,10 +1802,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1858,31 +1849,31 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -1935,37 +1926,37 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>5</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2012,22 +2003,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2045,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2089,40 +2080,40 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2166,25 +2157,25 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2199,7 +2190,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2243,22 +2234,22 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2320,40 +2311,40 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2397,40 +2388,40 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>6</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2474,31 +2465,31 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2551,22 +2542,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2584,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2628,28 +2619,28 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2658,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2705,25 +2696,25 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -2732,13 +2723,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2782,28 +2773,28 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2859,28 +2850,28 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -2892,7 +2883,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3046,7 +3037,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3105,19 +3096,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O5">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>97.5</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
-        <v>96.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3223,10 +3214,10 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>80</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3282,22 +3273,22 @@
         <v>82</v>
       </c>
       <c r="N8">
-        <v>95</v>
+        <v>96.5</v>
       </c>
       <c r="O8">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="R8">
         <v>85</v>
       </c>
-      <c r="P8">
-        <v>100</v>
-      </c>
-      <c r="Q8">
-        <v>97.5</v>
-      </c>
-      <c r="R8">
-        <v>78.2</v>
-      </c>
       <c r="S8">
-        <v>82</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3341,7 +3332,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3459,10 +3450,10 @@
         <v>70</v>
       </c>
       <c r="N11">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O11">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3471,10 +3462,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="S11">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3530,10 +3521,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3577,10 +3568,10 @@
         <v>94</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O13">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3592,7 +3583,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3636,22 +3627,22 @@
         <v>76</v>
       </c>
       <c r="N14">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O14">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
-        <v>76</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3695,22 +3686,22 @@
         <v>70</v>
       </c>
       <c r="N15">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R15">
         <v>95</v>
       </c>
-      <c r="R15">
-        <v>92.7</v>
-      </c>
       <c r="S15">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3754,22 +3745,22 @@
         <v>34</v>
       </c>
       <c r="N16">
-        <v>25</v>
+        <v>17.6</v>
       </c>
       <c r="O16">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="P16">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q16">
-        <v>8.800000000000001</v>
+        <v>43</v>
       </c>
       <c r="R16">
-        <v>34.5</v>
+        <v>23.8</v>
       </c>
       <c r="S16">
-        <v>34</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3813,10 +3804,10 @@
         <v>90</v>
       </c>
       <c r="N17">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O17">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -3825,7 +3816,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="S17">
         <v>90</v>
@@ -3872,22 +3863,22 @@
         <v>90</v>
       </c>
       <c r="N18">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="O18">
-        <v>67.5</v>
+        <v>42.2</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R18">
-        <v>78.2</v>
+        <v>82.5</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3931,22 +3922,22 @@
         <v>72</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O19">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R19">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S19">
-        <v>72</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4049,10 +4040,10 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="O21">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4061,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4108,13 +4099,13 @@
         <v>86</v>
       </c>
       <c r="N22">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4123,7 +4114,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4179,7 +4170,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4235,10 +4226,10 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4285,22 +4276,22 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O25">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R25">
-        <v>76.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4347,16 +4338,16 @@
         <v>100</v>
       </c>
       <c r="O26">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="R26">
         <v>95</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>97.5</v>
-      </c>
-      <c r="R26">
-        <v>96.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4462,16 +4453,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4521,22 +4512,22 @@
         <v>90</v>
       </c>
       <c r="N29">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="O29">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S29">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4580,22 +4571,22 @@
         <v>90</v>
       </c>
       <c r="N30">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O30">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4654,7 +4645,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
   </sheetData>
@@ -4720,16 +4711,16 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -4743,7 +4734,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -4752,19 +4743,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4775,7 +4766,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -4784,19 +4775,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4807,7 +4798,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -4816,19 +4807,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>85.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>14.3</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4860,7 +4851,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4892,7 +4883,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4974,16 +4965,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920190</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4997,22 +4988,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920190</v>
+        <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5020,22 +5011,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5043,22 +5034,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5066,16 +5057,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920209</v>
+        <v>21330051920203</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5089,19 +5080,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920209</v>
+        <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -5112,16 +5103,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5135,22 +5126,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920212</v>
+        <v>21330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5158,16 +5149,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920214</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
